--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,12 +777,134 @@
       <c r="AZ2" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136685456</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137282806</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92580</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567502</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6684895</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282806</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136685456</v>
       </c>
       <c r="B2" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48381-2025 artfynd.xlsx
+++ b/artfynd/A 48381-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137282806</v>
       </c>
       <c r="B3" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
